--- a/resources/spc_sheet_oos_decoration.xlsx
+++ b/resources/spc_sheet_oos_decoration.xlsx
@@ -10892,7 +10892,7 @@
         <v>-7.6155</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01529912280701755</v>
+        <v>0.01529912280701754</v>
       </c>
       <c r="J3" t="n">
         <v>6.5</v>
@@ -11210,7 +11210,7 @@
         <v>-3.4499</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.04229736842105266</v>
+        <v>-0.04229736842105263</v>
       </c>
       <c r="J9" t="n">
         <v>6.5</v>
@@ -11899,7 +11899,7 @@
         <v>-6.8108</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.07766140350877195</v>
+        <v>-0.07766140350877193</v>
       </c>
       <c r="J22" t="n">
         <v>6.5</v>
@@ -12058,7 +12058,7 @@
         <v>-4.1055</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4946271929824562</v>
+        <v>0.4946271929824561</v>
       </c>
       <c r="J25" t="n">
         <v>6.5</v>
@@ -12482,7 +12482,7 @@
         <v>-6.2914</v>
       </c>
       <c r="I33" t="n">
-        <v>0.03470701754385964</v>
+        <v>0.03470701754385961</v>
       </c>
       <c r="J33" t="n">
         <v>6.5</v>
@@ -12535,7 +12535,7 @@
         <v>-5.1599</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4605105263157895</v>
+        <v>-0.4605105263157894</v>
       </c>
       <c r="J34" t="n">
         <v>6.5</v>
@@ -13118,7 +13118,7 @@
         <v>-4.4651</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.04652807017543856</v>
+        <v>-0.04652807017543861</v>
       </c>
       <c r="J45" t="n">
         <v>6.5</v>
@@ -13277,7 +13277,7 @@
         <v>-5.8719</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3151008771929824</v>
+        <v>0.3151008771929825</v>
       </c>
       <c r="J48" t="n">
         <v>6.5</v>
@@ -13542,7 +13542,7 @@
         <v>-8.343400000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.8040798245614035</v>
+        <v>-0.8040798245614036</v>
       </c>
       <c r="J53" t="n">
         <v>6.5</v>
@@ -13860,7 +13860,7 @@
         <v>-6.9804</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.008550000000000026</v>
+        <v>-0.008550000000000058</v>
       </c>
       <c r="J59" t="n">
         <v>6.5</v>
@@ -14549,7 +14549,7 @@
         <v>-4.5534</v>
       </c>
       <c r="I72" t="n">
-        <v>0.6093447368421052</v>
+        <v>0.6093447368421053</v>
       </c>
       <c r="J72" t="n">
         <v>6.5</v>
@@ -14708,7 +14708,7 @@
         <v>-5.7729</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2905122807017543</v>
+        <v>0.2905122807017544</v>
       </c>
       <c r="J75" t="n">
         <v>6.5</v>
@@ -14814,7 +14814,7 @@
         <v>-4.8514</v>
       </c>
       <c r="I77" t="n">
-        <v>1.477787719298246</v>
+        <v>1.477787719298245</v>
       </c>
       <c r="J77" t="n">
         <v>6.5</v>
@@ -14973,7 +14973,7 @@
         <v>-5.8919</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.006774561403508777</v>
+        <v>-0.006774561403508803</v>
       </c>
       <c r="J80" t="n">
         <v>6.5</v>
@@ -15079,7 +15079,7 @@
         <v>-5.2636</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.09407280701754382</v>
+        <v>-0.09407280701754384</v>
       </c>
       <c r="J82" t="n">
         <v>6.5</v>
@@ -15397,7 +15397,7 @@
         <v>-6.3484</v>
       </c>
       <c r="I88" t="n">
-        <v>0.09611228070175443</v>
+        <v>0.0961122807017544</v>
       </c>
       <c r="J88" t="n">
         <v>6.5</v>
@@ -15874,7 +15874,7 @@
         <v>-6.9829</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.6455096491228069</v>
+        <v>-0.6455096491228072</v>
       </c>
       <c r="J97" t="n">
         <v>6.5</v>
@@ -16351,7 +16351,7 @@
         <v>-4.4856</v>
       </c>
       <c r="I106" t="n">
-        <v>0.496932456140351</v>
+        <v>0.4969324561403509</v>
       </c>
       <c r="J106" t="n">
         <v>6.5</v>
@@ -16775,7 +16775,7 @@
         <v>-8.3277</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.9198491228070176</v>
+        <v>-0.9198491228070175</v>
       </c>
       <c r="J114" t="n">
         <v>6.5</v>
@@ -16934,7 +16934,7 @@
         <v>-4.0971</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5978482456140352</v>
+        <v>0.597848245614035</v>
       </c>
       <c r="J117" t="n">
         <v>6.5</v>
@@ -17040,7 +17040,7 @@
         <v>-5.0645</v>
       </c>
       <c r="I119" t="n">
-        <v>0.03353596491228069</v>
+        <v>0.03353596491228068</v>
       </c>
       <c r="J119" t="n">
         <v>6.5</v>
@@ -17252,7 +17252,7 @@
         <v>-6.1071</v>
       </c>
       <c r="I123" t="n">
-        <v>0.06978508771929821</v>
+        <v>0.06978508771929823</v>
       </c>
       <c r="J123" t="n">
         <v>6.5</v>
@@ -17782,7 +17782,7 @@
         <v>-4.3932</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8818175438596491</v>
+        <v>0.8818175438596492</v>
       </c>
       <c r="J133" t="n">
         <v>6.5</v>
@@ -18577,7 +18577,7 @@
         <v>-6.718</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5547491228070176</v>
+        <v>0.5547491228070175</v>
       </c>
       <c r="J148" t="n">
         <v>6.5</v>
@@ -18736,7 +18736,7 @@
         <v>-5.6271</v>
       </c>
       <c r="I151" t="n">
-        <v>0.8492342105263158</v>
+        <v>0.8492342105263159</v>
       </c>
       <c r="J151" t="n">
         <v>6.5</v>
@@ -19001,7 +19001,7 @@
         <v>-25.5842</v>
       </c>
       <c r="I156" t="n">
-        <v>0.9268140350877192</v>
+        <v>0.9268140350877193</v>
       </c>
       <c r="J156" t="n">
         <v>6.5</v>
@@ -19213,7 +19213,7 @@
         <v>-6.347</v>
       </c>
       <c r="I160" t="n">
-        <v>0.9459850877192983</v>
+        <v>0.9459850877192982</v>
       </c>
       <c r="J160" t="n">
         <v>6.5</v>
@@ -19531,7 +19531,7 @@
         <v>-5.6733</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.1435087719298246</v>
+        <v>-0.1435087719298245</v>
       </c>
       <c r="J166" t="n">
         <v>6.5</v>
@@ -20167,7 +20167,7 @@
         <v>-14.0222</v>
       </c>
       <c r="I178" t="n">
-        <v>0.8890823008849558</v>
+        <v>0.8890823008849557</v>
       </c>
       <c r="J178" t="n">
         <v>6.5</v>
@@ -20909,7 +20909,7 @@
         <v>-7.7786</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.3039491228070175</v>
+        <v>-0.3039491228070176</v>
       </c>
       <c r="J192" t="n">
         <v>6.5</v>
@@ -21280,7 +21280,7 @@
         <v>-6.6293</v>
       </c>
       <c r="I199" t="n">
-        <v>0.9794122807017543</v>
+        <v>0.9794122807017545</v>
       </c>
       <c r="J199" t="n">
         <v>6.5</v>
@@ -21916,7 +21916,7 @@
         <v>-7.2617</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.005909649122807063</v>
+        <v>-0.00590964912280703</v>
       </c>
       <c r="J211" t="n">
         <v>6.5</v>
@@ -22075,7 +22075,7 @@
         <v>-7.7634</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.07643596491228072</v>
+        <v>-0.07643596491228073</v>
       </c>
       <c r="J214" t="n">
         <v>6.5</v>
@@ -23400,7 +23400,7 @@
         <v>-6.5046</v>
       </c>
       <c r="I239" t="n">
-        <v>0.7791377192982457</v>
+        <v>0.7791377192982456</v>
       </c>
       <c r="J239" t="n">
         <v>6.5</v>
@@ -23771,7 +23771,7 @@
         <v>-4.9538</v>
       </c>
       <c r="I246" t="n">
-        <v>0.614871052631579</v>
+        <v>0.6148710526315789</v>
       </c>
       <c r="J246" t="n">
         <v>6.5</v>
@@ -23983,7 +23983,7 @@
         <v>-6.1278</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.0579815789473684</v>
+        <v>-0.05798157894736843</v>
       </c>
       <c r="J250" t="n">
         <v>6.5</v>
@@ -25149,7 +25149,7 @@
         <v>-5.5515</v>
       </c>
       <c r="I272" t="n">
-        <v>0.3501815789473685</v>
+        <v>0.3501815789473684</v>
       </c>
       <c r="J272" t="n">
         <v>6.5</v>
@@ -25202,7 +25202,7 @@
         <v>-6.2885</v>
       </c>
       <c r="I273" t="n">
-        <v>0.04088859649122807</v>
+        <v>0.04088859649122806</v>
       </c>
       <c r="J273" t="n">
         <v>6.5</v>
@@ -25308,7 +25308,7 @@
         <v>-6.532</v>
       </c>
       <c r="I275" t="n">
-        <v>0.01685877192982452</v>
+        <v>0.01685877192982455</v>
       </c>
       <c r="J275" t="n">
         <v>6.5</v>
@@ -25361,7 +25361,7 @@
         <v>-8.580500000000001</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.4958578947368421</v>
+        <v>-0.4958578947368422</v>
       </c>
       <c r="J276" t="n">
         <v>6.5</v>
@@ -25520,7 +25520,7 @@
         <v>-6.6815</v>
       </c>
       <c r="I279" t="n">
-        <v>0.3845070175438596</v>
+        <v>0.3845070175438597</v>
       </c>
       <c r="J279" t="n">
         <v>6.5</v>
@@ -26103,7 +26103,7 @@
         <v>-6.1323</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2874561403508771</v>
+        <v>-0.2874561403508772</v>
       </c>
       <c r="J290" t="n">
         <v>6.5</v>
@@ -26209,7 +26209,7 @@
         <v>-3.3104</v>
       </c>
       <c r="I292" t="n">
-        <v>0.8435719298245615</v>
+        <v>0.8435719298245613</v>
       </c>
       <c r="J292" t="n">
         <v>6.5</v>
@@ -26527,7 +26527,7 @@
         <v>-6.2062</v>
       </c>
       <c r="I298" t="n">
-        <v>0.3236368421052631</v>
+        <v>0.3236368421052632</v>
       </c>
       <c r="J298" t="n">
         <v>6.5</v>
@@ -26633,7 +26633,7 @@
         <v>-4.3444</v>
       </c>
       <c r="I300" t="n">
-        <v>0.6657157894736841</v>
+        <v>0.6657157894736843</v>
       </c>
       <c r="J300" t="n">
         <v>6.5</v>
@@ -28011,7 +28011,7 @@
         <v>-6.5794</v>
       </c>
       <c r="I326" t="n">
-        <v>0.4163964912280703</v>
+        <v>0.4163964912280702</v>
       </c>
       <c r="J326" t="n">
         <v>6.5</v>
@@ -29389,7 +29389,7 @@
         <v>-6.3705</v>
       </c>
       <c r="I352" t="n">
-        <v>0.09694385964912278</v>
+        <v>0.09694385964912279</v>
       </c>
       <c r="J352" t="n">
         <v>6.5</v>
@@ -31085,7 +31085,7 @@
         <v>-5.9691</v>
       </c>
       <c r="I384" t="n">
-        <v>-0.09673684210526313</v>
+        <v>-0.09673684210526315</v>
       </c>
       <c r="J384" t="n">
         <v>6.5</v>
@@ -31933,7 +31933,7 @@
         <v>-7.181</v>
       </c>
       <c r="I400" t="n">
-        <v>0.2636938596491228</v>
+        <v>0.2636938596491227</v>
       </c>
       <c r="J400" t="n">
         <v>6.5</v>
@@ -34053,7 +34053,7 @@
         <v>-8.6503</v>
       </c>
       <c r="I440" t="n">
-        <v>0.04960877192982458</v>
+        <v>0.04960877192982456</v>
       </c>
       <c r="J440" t="n">
         <v>6.5</v>
@@ -34318,7 +34318,7 @@
         <v>-7.706</v>
       </c>
       <c r="I445" t="n">
-        <v>-0.01646666666666669</v>
+        <v>-0.0164666666666667</v>
       </c>
       <c r="J445" t="n">
         <v>6.5</v>
@@ -34795,7 +34795,7 @@
         <v>-7.3081</v>
       </c>
       <c r="I454" t="n">
-        <v>0.06260964912280706</v>
+        <v>0.06260964912280703</v>
       </c>
       <c r="J454" t="n">
         <v>6.5</v>
@@ -34901,7 +34901,7 @@
         <v>-5.8034</v>
       </c>
       <c r="I456" t="n">
-        <v>0.01259649122807016</v>
+        <v>0.01259649122807015</v>
       </c>
       <c r="J456" t="n">
         <v>6.5</v>
@@ -35537,7 +35537,7 @@
         <v>-6.4277</v>
       </c>
       <c r="I468" t="n">
-        <v>0.562111403508772</v>
+        <v>0.5621114035087719</v>
       </c>
       <c r="J468" t="n">
         <v>6.5</v>

--- a/resources/spc_sheet_oos_decoration.xlsx
+++ b/resources/spc_sheet_oos_decoration.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M678" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z517" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z571" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M626" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M673" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="M678" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Z517" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Z571" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="M626" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="M673" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -847,7 +847,7 @@
         <v>-3.0885</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01310789473684212</v>
+        <v>0.0131078947368421</v>
       </c>
       <c r="J8" t="n">
         <v>6</v>
@@ -1271,7 +1271,7 @@
         <v>-4.8336</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3281973684210526</v>
+        <v>-0.3281973684210527</v>
       </c>
       <c r="J16" t="n">
         <v>6</v>
@@ -1324,7 +1324,7 @@
         <v>-6.6533</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9426131578947369</v>
+        <v>-0.9426131578947368</v>
       </c>
       <c r="J17" t="n">
         <v>6</v>
@@ -1536,7 +1536,7 @@
         <v>-6.55</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3553368421052631</v>
+        <v>-0.3553368421052632</v>
       </c>
       <c r="J21" t="n">
         <v>6</v>
@@ -1801,7 +1801,7 @@
         <v>-3.9705</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.09232807017543861</v>
+        <v>-0.09232807017543858</v>
       </c>
       <c r="J26" t="n">
         <v>6</v>
@@ -2225,7 +2225,7 @@
         <v>-7.2604</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.400568421052632</v>
+        <v>-1.400568421052631</v>
       </c>
       <c r="J34" t="n">
         <v>6</v>
@@ -2543,7 +2543,7 @@
         <v>-6.0781</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.6418736842105263</v>
+        <v>-0.6418736842105264</v>
       </c>
       <c r="J40" t="n">
         <v>6</v>
@@ -2808,7 +2808,7 @@
         <v>-9.6312</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4071991228070175</v>
+        <v>0.4071991228070176</v>
       </c>
       <c r="J45" t="n">
         <v>6</v>
@@ -2861,7 +2861,7 @@
         <v>-3.5591</v>
       </c>
       <c r="I46" t="n">
-        <v>0.5819008771929826</v>
+        <v>0.5819008771929824</v>
       </c>
       <c r="J46" t="n">
         <v>6</v>
@@ -2967,7 +2967,7 @@
         <v>-5.6767</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.03293684210526314</v>
+        <v>-0.03293684210526316</v>
       </c>
       <c r="J48" t="n">
         <v>6</v>
@@ -3126,7 +3126,7 @@
         <v>-8.3728</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8894815789473685</v>
+        <v>0.8894815789473683</v>
       </c>
       <c r="J51" t="n">
         <v>6</v>
@@ -3338,7 +3338,7 @@
         <v>-4.3863</v>
       </c>
       <c r="I55" t="n">
-        <v>0.05978508771929825</v>
+        <v>0.05978508771929823</v>
       </c>
       <c r="J55" t="n">
         <v>6</v>
@@ -4345,7 +4345,7 @@
         <v>-5.1932</v>
       </c>
       <c r="I74" t="n">
-        <v>0.04012719298245613</v>
+        <v>0.04012719298245614</v>
       </c>
       <c r="J74" t="n">
         <v>6</v>
@@ -4610,7 +4610,7 @@
         <v>-5.6846</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.06024385964912281</v>
+        <v>-0.06024385964912282</v>
       </c>
       <c r="J79" t="n">
         <v>6</v>
@@ -4875,7 +4875,7 @@
         <v>-4.9933</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.3644131578947368</v>
+        <v>-0.3644131578947369</v>
       </c>
       <c r="J84" t="n">
         <v>6</v>
@@ -5405,7 +5405,7 @@
         <v>-4.3387</v>
       </c>
       <c r="I94" t="n">
-        <v>0.07310614035087722</v>
+        <v>0.0731061403508772</v>
       </c>
       <c r="J94" t="n">
         <v>6</v>
@@ -5458,7 +5458,7 @@
         <v>-4.2277</v>
       </c>
       <c r="I95" t="n">
-        <v>0.04920350877192986</v>
+        <v>0.04920350877192983</v>
       </c>
       <c r="J95" t="n">
         <v>6</v>
@@ -5511,7 +5511,7 @@
         <v>-2.9467</v>
       </c>
       <c r="I96" t="n">
-        <v>0.8123438596491228</v>
+        <v>0.8123438596491227</v>
       </c>
       <c r="J96" t="n">
         <v>6</v>
@@ -6094,7 +6094,7 @@
         <v>-3.4868</v>
       </c>
       <c r="I107" t="n">
-        <v>0.7402166666666666</v>
+        <v>0.7402166666666667</v>
       </c>
       <c r="J107" t="n">
         <v>6</v>
@@ -6571,7 +6571,7 @@
         <v>-3.4303</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.1385447368421053</v>
+        <v>-0.1385447368421052</v>
       </c>
       <c r="J116" t="n">
         <v>6</v>
@@ -6783,7 +6783,7 @@
         <v>-3.7796</v>
       </c>
       <c r="I120" t="n">
-        <v>0.04655438596491228</v>
+        <v>0.04655438596491227</v>
       </c>
       <c r="J120" t="n">
         <v>6</v>
@@ -7419,7 +7419,7 @@
         <v>-7.5938</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.4827324561403509</v>
+        <v>-0.4827324561403508</v>
       </c>
       <c r="J132" t="n">
         <v>6</v>
@@ -7578,7 +7578,7 @@
         <v>-4.7859</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0269017543859649</v>
+        <v>-0.02690175438596493</v>
       </c>
       <c r="J135" t="n">
         <v>6</v>
@@ -7684,7 +7684,7 @@
         <v>-3.5278</v>
       </c>
       <c r="I137" t="n">
-        <v>0.7379815789473684</v>
+        <v>0.7379815789473685</v>
       </c>
       <c r="J137" t="n">
         <v>6</v>
@@ -8108,7 +8108,7 @@
         <v>-4.6064</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4024736842105263</v>
+        <v>-0.4024736842105264</v>
       </c>
       <c r="J145" t="n">
         <v>6</v>
@@ -8320,7 +8320,7 @@
         <v>-5.6437</v>
       </c>
       <c r="I149" t="n">
-        <v>0.09282894736842105</v>
+        <v>0.09282894736842107</v>
       </c>
       <c r="J149" t="n">
         <v>6</v>
@@ -8956,7 +8956,7 @@
         <v>-5.6246</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.673040350877193</v>
+        <v>-0.6730403508771929</v>
       </c>
       <c r="J161" t="n">
         <v>6</v>
@@ -9062,7 +9062,7 @@
         <v>-6.0523</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.2121008771929825</v>
+        <v>-0.2121008771929824</v>
       </c>
       <c r="J163" t="n">
         <v>6</v>
@@ -9327,7 +9327,7 @@
         <v>-5.8161</v>
       </c>
       <c r="I168" t="n">
-        <v>2.603806140350877</v>
+        <v>2.603806140350878</v>
       </c>
       <c r="J168" t="n">
         <v>6</v>
@@ -9380,7 +9380,7 @@
         <v>-8.9049</v>
       </c>
       <c r="I169" t="n">
-        <v>0.07020701754385963</v>
+        <v>0.07020701754385966</v>
       </c>
       <c r="J169" t="n">
         <v>6</v>
@@ -10493,7 +10493,7 @@
         <v>-8.2218</v>
       </c>
       <c r="I190" t="n">
-        <v>0.08150438596491227</v>
+        <v>0.08150438596491229</v>
       </c>
       <c r="J190" t="n">
         <v>6</v>
@@ -10811,7 +10811,7 @@
         <v>-5.6842</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4003035087719299</v>
+        <v>-0.4003035087719298</v>
       </c>
       <c r="J196" t="n">
         <v>6</v>
@@ -11129,7 +11129,7 @@
         <v>-7.2497</v>
       </c>
       <c r="I202" t="n">
-        <v>0.07138947368421053</v>
+        <v>0.07138947368421056</v>
       </c>
       <c r="J202" t="n">
         <v>6</v>
@@ -11447,7 +11447,7 @@
         <v>-4.9757</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.003107894736842106</v>
+        <v>-0.003107894736842108</v>
       </c>
       <c r="J208" t="n">
         <v>6</v>
@@ -11606,7 +11606,7 @@
         <v>-6.3242</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4850437500000001</v>
+        <v>-0.48504375</v>
       </c>
       <c r="J211" t="n">
         <v>6</v>
@@ -11659,7 +11659,7 @@
         <v>-6.6343</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.03756929824561402</v>
+        <v>-0.03756929824561403</v>
       </c>
       <c r="J212" t="n">
         <v>6</v>
@@ -12560,7 +12560,7 @@
         <v>-3.7281</v>
       </c>
       <c r="I229" t="n">
-        <v>0.7234912280701755</v>
+        <v>0.7234912280701754</v>
       </c>
       <c r="J229" t="n">
         <v>6</v>
@@ -12984,7 +12984,7 @@
         <v>-6.3979</v>
       </c>
       <c r="I237" t="n">
-        <v>-1.575316666666667</v>
+        <v>-1.575316666666666</v>
       </c>
       <c r="J237" t="n">
         <v>6</v>
@@ -13461,7 +13461,7 @@
         <v>-6.8972</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.07318070175438597</v>
+        <v>-0.07318070175438596</v>
       </c>
       <c r="J246" t="n">
         <v>6</v>
@@ -14044,7 +14044,7 @@
         <v>-5.3167</v>
       </c>
       <c r="I257" t="n">
-        <v>0.2733131578947368</v>
+        <v>0.2733131578947369</v>
       </c>
       <c r="J257" t="n">
         <v>6</v>
@@ -14733,7 +14733,7 @@
         <v>-7.6472</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4999350877192983</v>
+        <v>-0.4999350877192982</v>
       </c>
       <c r="J270" t="n">
         <v>6</v>
@@ -15793,7 +15793,7 @@
         <v>-7.0668</v>
       </c>
       <c r="I290" t="n">
-        <v>0.06098684210526315</v>
+        <v>0.06098684210526317</v>
       </c>
       <c r="J290" t="n">
         <v>6</v>
@@ -16111,7 +16111,7 @@
         <v>-5.6525</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.05103859649122806</v>
+        <v>-0.05103859649122804</v>
       </c>
       <c r="J296" t="n">
         <v>6</v>
@@ -18337,7 +18337,7 @@
         <v>-6.2446</v>
       </c>
       <c r="I338" t="n">
-        <v>0.02668684210526317</v>
+        <v>0.02668684210526319</v>
       </c>
       <c r="J338" t="n">
         <v>6</v>
@@ -18708,7 +18708,7 @@
         <v>-4.6724</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.155069298245614</v>
+        <v>-0.1550692982456141</v>
       </c>
       <c r="J345" t="n">
         <v>6</v>
@@ -21305,7 +21305,7 @@
         <v>-4.1648</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.02278245614035089</v>
+        <v>-0.0227824561403509</v>
       </c>
       <c r="J394" t="n">
         <v>6</v>
@@ -22365,7 +22365,7 @@
         <v>-4.6525</v>
       </c>
       <c r="I414" t="n">
-        <v>0.8355842105263158</v>
+        <v>0.8355842105263157</v>
       </c>
       <c r="J414" t="n">
         <v>6</v>
@@ -22683,7 +22683,7 @@
         <v>-3.3894</v>
       </c>
       <c r="I420" t="n">
-        <v>1.188629824561403</v>
+        <v>1.188629824561404</v>
       </c>
       <c r="J420" t="n">
         <v>6</v>
@@ -55922,7 +55922,7 @@
         <v>-3.1139</v>
       </c>
       <c r="I2" t="n">
-        <v>0.130678947368421</v>
+        <v>0.1306789473684211</v>
       </c>
       <c r="J2" t="n">
         <v>6.5</v>
@@ -56134,7 +56134,7 @@
         <v>-7.3392</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.05725964912280702</v>
+        <v>-0.057259649122807</v>
       </c>
       <c r="J6" t="n">
         <v>6.5</v>
@@ -56876,7 +56876,7 @@
         <v>-6.8108</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.07766140350877195</v>
+        <v>-0.07766140350877193</v>
       </c>
       <c r="J20" t="n">
         <v>6.5</v>
@@ -57247,7 +57247,7 @@
         <v>-5.8719</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3151008771929824</v>
+        <v>0.3151008771929825</v>
       </c>
       <c r="J27" t="n">
         <v>6.5</v>
@@ -57830,7 +57830,7 @@
         <v>-6.9804</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.008549999999999995</v>
+        <v>-0.008550000000000004</v>
       </c>
       <c r="J38" t="n">
         <v>6.5</v>
@@ -57989,7 +57989,7 @@
         <v>-5.5468</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.0523719298245614</v>
+        <v>-0.05237192982456143</v>
       </c>
       <c r="J41" t="n">
         <v>6.5</v>
@@ -58307,7 +58307,7 @@
         <v>-5.5309</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.5048745614035087</v>
+        <v>-0.5048745614035088</v>
       </c>
       <c r="J47" t="n">
         <v>6.5</v>
@@ -58943,7 +58943,7 @@
         <v>-5.8919</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.006774561403508777</v>
+        <v>-0.006774561403508735</v>
       </c>
       <c r="J59" t="n">
         <v>6.5</v>
@@ -59049,7 +59049,7 @@
         <v>-5.2636</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.09407280701754384</v>
+        <v>-0.09407280701754381</v>
       </c>
       <c r="J61" t="n">
         <v>6.5</v>
@@ -59367,7 +59367,7 @@
         <v>-6.3484</v>
       </c>
       <c r="I67" t="n">
-        <v>0.09611228070175441</v>
+        <v>0.09611228070175443</v>
       </c>
       <c r="J67" t="n">
         <v>6.5</v>
@@ -59579,7 +59579,7 @@
         <v>-9.1792</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3775017543859648</v>
+        <v>-0.3775017543859649</v>
       </c>
       <c r="J71" t="n">
         <v>6.5</v>
@@ -60321,7 +60321,7 @@
         <v>-4.4856</v>
       </c>
       <c r="I85" t="n">
-        <v>0.4969324561403509</v>
+        <v>0.496932456140351</v>
       </c>
       <c r="J85" t="n">
         <v>6.5</v>
@@ -60480,7 +60480,7 @@
         <v>-7.0988</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.02176052631578946</v>
+        <v>-0.02176052631578949</v>
       </c>
       <c r="J88" t="n">
         <v>6.5</v>
@@ -60745,7 +60745,7 @@
         <v>-4.0971</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5978482456140352</v>
+        <v>0.597848245614035</v>
       </c>
       <c r="J93" t="n">
         <v>6.5</v>
@@ -60851,7 +60851,7 @@
         <v>-5.0645</v>
       </c>
       <c r="I95" t="n">
-        <v>0.0335359649122807</v>
+        <v>0.03353596491228066</v>
       </c>
       <c r="J95" t="n">
         <v>6.5</v>
@@ -61063,7 +61063,7 @@
         <v>-6.1071</v>
       </c>
       <c r="I99" t="n">
-        <v>0.06978508771929824</v>
+        <v>0.06978508771929826</v>
       </c>
       <c r="J99" t="n">
         <v>6.5</v>
@@ -61540,7 +61540,7 @@
         <v>-5.6271</v>
       </c>
       <c r="I108" t="n">
-        <v>0.8492342105263159</v>
+        <v>0.8492342105263158</v>
       </c>
       <c r="J108" t="n">
         <v>6.5</v>
@@ -61805,7 +61805,7 @@
         <v>-25.5842</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9268140350877192</v>
+        <v>0.9268140350877193</v>
       </c>
       <c r="J113" t="n">
         <v>6.5</v>
@@ -61858,7 +61858,7 @@
         <v>-7.8913</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1640561403508772</v>
+        <v>0.1640561403508771</v>
       </c>
       <c r="J114" t="n">
         <v>6.5</v>
@@ -62335,7 +62335,7 @@
         <v>-5.6733</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.1435087719298245</v>
+        <v>-0.1435087719298246</v>
       </c>
       <c r="J123" t="n">
         <v>6.5</v>
@@ -63342,7 +63342,7 @@
         <v>-7.3019</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1687754385964913</v>
+        <v>0.1687754385964912</v>
       </c>
       <c r="J142" t="n">
         <v>6.5</v>
@@ -63448,7 +63448,7 @@
         <v>-7.2321</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1916350877192983</v>
+        <v>0.1916350877192982</v>
       </c>
       <c r="J144" t="n">
         <v>6.5</v>
@@ -65303,7 +65303,7 @@
         <v>-4.9538</v>
       </c>
       <c r="I179" t="n">
-        <v>0.6148710526315789</v>
+        <v>0.614871052631579</v>
       </c>
       <c r="J179" t="n">
         <v>6.5</v>
@@ -66310,7 +66310,7 @@
         <v>-5.8156</v>
       </c>
       <c r="I198" t="n">
-        <v>0.3542000000000001</v>
+        <v>0.3542</v>
       </c>
       <c r="J198" t="n">
         <v>6.5</v>
@@ -66522,7 +66522,7 @@
         <v>-7.4049</v>
       </c>
       <c r="I202" t="n">
-        <v>0.5309342105263158</v>
+        <v>0.5309342105263157</v>
       </c>
       <c r="J202" t="n">
         <v>6.5</v>
@@ -66734,7 +66734,7 @@
         <v>-6.2885</v>
       </c>
       <c r="I206" t="n">
-        <v>0.04088859649122803</v>
+        <v>0.04088859649122807</v>
       </c>
       <c r="J206" t="n">
         <v>6.5</v>
@@ -66840,7 +66840,7 @@
         <v>-6.532</v>
       </c>
       <c r="I208" t="n">
-        <v>0.01685877192982456</v>
+        <v>0.01685877192982455</v>
       </c>
       <c r="J208" t="n">
         <v>6.5</v>
@@ -67105,7 +67105,7 @@
         <v>-5.9134</v>
       </c>
       <c r="I213" t="n">
-        <v>0.6087508771929824</v>
+        <v>0.6087508771929826</v>
       </c>
       <c r="J213" t="n">
         <v>6.5</v>
@@ -67635,7 +67635,7 @@
         <v>-6.1323</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.2874561403508772</v>
+        <v>-0.2874561403508771</v>
       </c>
       <c r="J223" t="n">
         <v>6.5</v>
@@ -68536,7 +68536,7 @@
         <v>-6.5794</v>
       </c>
       <c r="I240" t="n">
-        <v>0.4163964912280703</v>
+        <v>0.4163964912280702</v>
       </c>
       <c r="J240" t="n">
         <v>6.5</v>
@@ -69808,7 +69808,7 @@
         <v>-6.3672</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.05369473684210526</v>
+        <v>-0.05369473684210525</v>
       </c>
       <c r="J264" t="n">
         <v>6.5</v>
@@ -71822,7 +71822,7 @@
         <v>-6.8674</v>
       </c>
       <c r="I302" t="n">
-        <v>0.1219596491228071</v>
+        <v>0.121959649122807</v>
       </c>
       <c r="J302" t="n">
         <v>6.5</v>
@@ -72405,7 +72405,7 @@
         <v>-6.0546</v>
       </c>
       <c r="I313" t="n">
-        <v>0.8782254385964913</v>
+        <v>0.8782254385964914</v>
       </c>
       <c r="J313" t="n">
         <v>6.5</v>
@@ -73412,7 +73412,7 @@
         <v>-6.5834</v>
       </c>
       <c r="I332" t="n">
-        <v>0.9868701754385965</v>
+        <v>0.9868701754385966</v>
       </c>
       <c r="J332" t="n">
         <v>6.5</v>
@@ -73518,7 +73518,7 @@
         <v>-8.6503</v>
       </c>
       <c r="I334" t="n">
-        <v>0.04960877192982455</v>
+        <v>0.04960877192982457</v>
       </c>
       <c r="J334" t="n">
         <v>6.5</v>
@@ -73571,7 +73571,7 @@
         <v>-6.0654</v>
       </c>
       <c r="I335" t="n">
-        <v>0.1482815789473685</v>
+        <v>0.1482815789473684</v>
       </c>
       <c r="J335" t="n">
         <v>6.5</v>
@@ -73783,7 +73783,7 @@
         <v>-7.706</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.01646666666666668</v>
+        <v>-0.0164666666666667</v>
       </c>
       <c r="J339" t="n">
         <v>6.5</v>
@@ -74260,7 +74260,7 @@
         <v>-7.3081</v>
       </c>
       <c r="I348" t="n">
-        <v>0.06260964912280706</v>
+        <v>0.06260964912280705</v>
       </c>
       <c r="J348" t="n">
         <v>6.5</v>
@@ -74366,7 +74366,7 @@
         <v>-5.8034</v>
       </c>
       <c r="I350" t="n">
-        <v>0.01259649122807018</v>
+        <v>0.01259649122807016</v>
       </c>
       <c r="J350" t="n">
         <v>6.5</v>
@@ -74631,7 +74631,7 @@
         <v>-7.3134</v>
       </c>
       <c r="I355" t="n">
-        <v>0.5714289473684212</v>
+        <v>0.571428947368421</v>
       </c>
       <c r="J355" t="n">
         <v>6.5</v>
@@ -75002,7 +75002,7 @@
         <v>-6.4277</v>
       </c>
       <c r="I362" t="n">
-        <v>0.5621114035087719</v>
+        <v>0.562111403508772</v>
       </c>
       <c r="J362" t="n">
         <v>6.5</v>
